--- a/tiflow-bfarm/TMD-3109-ausbau-alte-authentisierung/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/TMD-3109-ausbau-alte-authentisierung/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T11:11:50+00:00</t>
+    <t>2026-05-11T05:31:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/TMD-3109-ausbau-alte-authentisierung/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/TMD-3109-ausbau-alte-authentisierung/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T05:31:42+00:00</t>
+    <t>2026-05-11T10:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/TMD-3109-ausbau-alte-authentisierung/1.0.0-draft/all-profiles.xlsx
+++ b/tiflow-bfarm/TMD-3109-ausbau-alte-authentisierung/1.0.0-draft/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T10:38:11+00:00</t>
+    <t>2026-05-11T12:42:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
